--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117617814</v>
+        <v>117617815</v>
       </c>
       <c r="B5" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527857</v>
+        <v>527885</v>
       </c>
       <c r="R5" t="n">
-        <v>7167609</v>
+        <v>7167588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117617815</v>
+        <v>117617814</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527885</v>
+        <v>527857</v>
       </c>
       <c r="R6" t="n">
-        <v>7167588</v>
+        <v>7167609</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117617763</v>
+        <v>117617760</v>
       </c>
       <c r="B2" t="n">
-        <v>97756</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527908</v>
+        <v>527651</v>
       </c>
       <c r="R2" t="n">
-        <v>7167670</v>
+        <v>7167777</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117617761</v>
+        <v>117617763</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527640</v>
+        <v>527908</v>
       </c>
       <c r="R3" t="n">
-        <v>7167763</v>
+        <v>7167670</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117617760</v>
+        <v>117617801</v>
       </c>
       <c r="B4" t="n">
         <v>78480</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527651</v>
+        <v>527821</v>
       </c>
       <c r="R4" t="n">
-        <v>7167777</v>
+        <v>7167822</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117617815</v>
+        <v>117617765</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>97756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527885</v>
+        <v>527909</v>
       </c>
       <c r="R5" t="n">
-        <v>7167588</v>
+        <v>7167663</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117617812</v>
+        <v>117617761</v>
       </c>
       <c r="B7" t="n">
-        <v>58130</v>
+        <v>78480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,43 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527870</v>
+        <v>527640</v>
       </c>
       <c r="R7" t="n">
-        <v>7167648</v>
+        <v>7167763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,17 +1340,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117617765</v>
+        <v>117617812</v>
       </c>
       <c r="B8" t="n">
-        <v>97756</v>
+        <v>58130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,22 +1363,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527909</v>
+        <v>527870</v>
       </c>
       <c r="R8" t="n">
-        <v>7167663</v>
+        <v>7167648</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117617801</v>
+        <v>117617773</v>
       </c>
       <c r="B9" t="n">
         <v>78480</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527821</v>
+        <v>527758</v>
       </c>
       <c r="R9" t="n">
-        <v>7167822</v>
+        <v>7167744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,14 +1569,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117617773</v>
+        <v>117617815</v>
       </c>
       <c r="B10" t="n">
         <v>78480</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527758</v>
+        <v>527885</v>
       </c>
       <c r="R10" t="n">
-        <v>7167744</v>
+        <v>7167588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Sven Bengtsson</t>
+          <t>Sven Bengtsson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117617760</v>
+        <v>117617801</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527651</v>
+        <v>527821</v>
       </c>
       <c r="R2" t="n">
-        <v>7167777</v>
+        <v>7167822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117617763</v>
+        <v>117617815</v>
       </c>
       <c r="B3" t="n">
-        <v>97756</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527908</v>
+        <v>527885</v>
       </c>
       <c r="R3" t="n">
-        <v>7167670</v>
+        <v>7167588</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117617801</v>
+        <v>117617763</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>97758</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527821</v>
+        <v>527908</v>
       </c>
       <c r="R4" t="n">
-        <v>7167822</v>
+        <v>7167670</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117617765</v>
+        <v>117617812</v>
       </c>
       <c r="B5" t="n">
-        <v>97756</v>
+        <v>58131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,22 +1027,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527909</v>
+        <v>527870</v>
       </c>
       <c r="R5" t="n">
-        <v>7167663</v>
+        <v>7167648</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117617814</v>
+        <v>117617760</v>
       </c>
       <c r="B6" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527857</v>
+        <v>527651</v>
       </c>
       <c r="R6" t="n">
-        <v>7167609</v>
+        <v>7167777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117617761</v>
+        <v>117617814</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527640</v>
+        <v>527857</v>
       </c>
       <c r="R7" t="n">
-        <v>7167763</v>
+        <v>7167609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,17 +1345,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117617812</v>
+        <v>117617773</v>
       </c>
       <c r="B8" t="n">
-        <v>58130</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527870</v>
+        <v>527758</v>
       </c>
       <c r="R8" t="n">
-        <v>7167648</v>
+        <v>7167744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117617773</v>
+        <v>117617765</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>97758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,41 +1476,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527758</v>
+        <v>527909</v>
       </c>
       <c r="R9" t="n">
-        <v>7167744</v>
+        <v>7167663</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117617815</v>
+        <v>117617761</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527885</v>
+        <v>527640</v>
       </c>
       <c r="R10" t="n">
-        <v>7167588</v>
+        <v>7167763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sven Bengtsson, Andreas Estensen</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118682465</v>
+        <v>118682186</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527352</v>
+        <v>527828</v>
       </c>
       <c r="R11" t="n">
-        <v>7167588</v>
+        <v>7167818</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118682840</v>
+        <v>118682465</v>
       </c>
       <c r="B12" t="n">
         <v>78484</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527463</v>
+        <v>527352</v>
       </c>
       <c r="R12" t="n">
-        <v>7167702</v>
+        <v>7167588</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682357</v>
+        <v>118682840</v>
       </c>
       <c r="B13" t="n">
         <v>78484</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527635</v>
+        <v>527463</v>
       </c>
       <c r="R13" t="n">
-        <v>7167757</v>
+        <v>7167702</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118682719</v>
+        <v>118682108</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527409</v>
+        <v>527477</v>
       </c>
       <c r="R14" t="n">
-        <v>7167618</v>
+        <v>7167550</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118682668</v>
+        <v>118682436</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527638</v>
+        <v>527722</v>
       </c>
       <c r="R15" t="n">
-        <v>7167796</v>
+        <v>7167844</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682186</v>
+        <v>118682719</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527828</v>
+        <v>527409</v>
       </c>
       <c r="R18" t="n">
-        <v>7167818</v>
+        <v>7167618</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118682403</v>
+        <v>118682668</v>
       </c>
       <c r="B19" t="n">
         <v>78484</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527525</v>
+        <v>527638</v>
       </c>
       <c r="R19" t="n">
-        <v>7167728</v>
+        <v>7167796</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118682108</v>
+        <v>118682403</v>
       </c>
       <c r="B20" t="n">
         <v>78484</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527477</v>
+        <v>527525</v>
       </c>
       <c r="R20" t="n">
-        <v>7167550</v>
+        <v>7167728</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118682436</v>
+        <v>118682357</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527722</v>
+        <v>527635</v>
       </c>
       <c r="R21" t="n">
-        <v>7167844</v>
+        <v>7167757</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -1799,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118682465</v>
+        <v>118682108</v>
       </c>
       <c r="B12" t="n">
         <v>78484</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527352</v>
+        <v>527477</v>
       </c>
       <c r="R12" t="n">
-        <v>7167588</v>
+        <v>7167550</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118682108</v>
+        <v>118682436</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527477</v>
+        <v>527722</v>
       </c>
       <c r="R14" t="n">
-        <v>7167550</v>
+        <v>7167844</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118682436</v>
+        <v>118682668</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527722</v>
+        <v>527638</v>
       </c>
       <c r="R15" t="n">
-        <v>7167844</v>
+        <v>7167796</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682328</v>
+        <v>118682357</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527763</v>
+        <v>527635</v>
       </c>
       <c r="R16" t="n">
-        <v>7167639</v>
+        <v>7167757</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118682060</v>
+        <v>118682328</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527491</v>
+        <v>527763</v>
       </c>
       <c r="R17" t="n">
-        <v>7167704</v>
+        <v>7167639</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682719</v>
+        <v>118682060</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527409</v>
+        <v>527491</v>
       </c>
       <c r="R18" t="n">
-        <v>7167618</v>
+        <v>7167704</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118682668</v>
+        <v>118682719</v>
       </c>
       <c r="B19" t="n">
         <v>78484</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527638</v>
+        <v>527409</v>
       </c>
       <c r="R19" t="n">
-        <v>7167796</v>
+        <v>7167618</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118682403</v>
+        <v>118682465</v>
       </c>
       <c r="B20" t="n">
         <v>78484</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527525</v>
+        <v>527352</v>
       </c>
       <c r="R20" t="n">
-        <v>7167728</v>
+        <v>7167588</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118682357</v>
+        <v>118682403</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527635</v>
+        <v>527525</v>
       </c>
       <c r="R21" t="n">
-        <v>7167757</v>
+        <v>7167728</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118682186</v>
+        <v>118682436</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527828</v>
+        <v>527722</v>
       </c>
       <c r="R11" t="n">
-        <v>7167818</v>
+        <v>7167844</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1802,7 +1802,7 @@
         <v>118682108</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682840</v>
+        <v>118682357</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527463</v>
+        <v>527635</v>
       </c>
       <c r="R13" t="n">
-        <v>7167702</v>
+        <v>7167757</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118682436</v>
+        <v>118682465</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527722</v>
+        <v>527352</v>
       </c>
       <c r="R14" t="n">
-        <v>7167844</v>
+        <v>7167588</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118682668</v>
+        <v>118682403</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527638</v>
+        <v>527525</v>
       </c>
       <c r="R15" t="n">
-        <v>7167796</v>
+        <v>7167728</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682357</v>
+        <v>118682719</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527635</v>
+        <v>527409</v>
       </c>
       <c r="R16" t="n">
-        <v>7167757</v>
+        <v>7167618</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118682328</v>
+        <v>118682186</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527763</v>
+        <v>527828</v>
       </c>
       <c r="R17" t="n">
-        <v>7167639</v>
+        <v>7167818</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682060</v>
+        <v>118682840</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527491</v>
+        <v>527463</v>
       </c>
       <c r="R18" t="n">
-        <v>7167704</v>
+        <v>7167702</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118682719</v>
+        <v>118682668</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527409</v>
+        <v>527638</v>
       </c>
       <c r="R19" t="n">
-        <v>7167618</v>
+        <v>7167796</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118682465</v>
+        <v>118682328</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527352</v>
+        <v>527763</v>
       </c>
       <c r="R20" t="n">
-        <v>7167588</v>
+        <v>7167639</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118682403</v>
+        <v>118682060</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527525</v>
+        <v>527491</v>
       </c>
       <c r="R21" t="n">
-        <v>7167728</v>
+        <v>7167704</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118682436</v>
+        <v>118682186</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527722</v>
+        <v>527828</v>
       </c>
       <c r="R11" t="n">
-        <v>7167844</v>
+        <v>7167818</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118682108</v>
+        <v>118682060</v>
       </c>
       <c r="B12" t="n">
         <v>78491</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527477</v>
+        <v>527491</v>
       </c>
       <c r="R12" t="n">
-        <v>7167550</v>
+        <v>7167704</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682357</v>
+        <v>118682108</v>
       </c>
       <c r="B13" t="n">
         <v>78491</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527635</v>
+        <v>527477</v>
       </c>
       <c r="R13" t="n">
-        <v>7167757</v>
+        <v>7167550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118682465</v>
+        <v>118682328</v>
       </c>
       <c r="B14" t="n">
         <v>78491</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527352</v>
+        <v>527763</v>
       </c>
       <c r="R14" t="n">
-        <v>7167588</v>
+        <v>7167639</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118682403</v>
+        <v>118682436</v>
       </c>
       <c r="B15" t="n">
         <v>78491</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527525</v>
+        <v>527722</v>
       </c>
       <c r="R15" t="n">
-        <v>7167728</v>
+        <v>7167844</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682719</v>
+        <v>118682357</v>
       </c>
       <c r="B16" t="n">
         <v>78491</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527409</v>
+        <v>527635</v>
       </c>
       <c r="R16" t="n">
-        <v>7167618</v>
+        <v>7167757</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118682186</v>
+        <v>118682840</v>
       </c>
       <c r="B17" t="n">
         <v>78491</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527828</v>
+        <v>527463</v>
       </c>
       <c r="R17" t="n">
-        <v>7167818</v>
+        <v>7167702</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682840</v>
+        <v>118682403</v>
       </c>
       <c r="B18" t="n">
         <v>78491</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527463</v>
+        <v>527525</v>
       </c>
       <c r="R18" t="n">
-        <v>7167702</v>
+        <v>7167728</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118682328</v>
+        <v>118682719</v>
       </c>
       <c r="B20" t="n">
         <v>78491</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527763</v>
+        <v>527409</v>
       </c>
       <c r="R20" t="n">
-        <v>7167639</v>
+        <v>7167618</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118682060</v>
+        <v>118682465</v>
       </c>
       <c r="B21" t="n">
         <v>78491</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527491</v>
+        <v>527352</v>
       </c>
       <c r="R21" t="n">
-        <v>7167704</v>
+        <v>7167588</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2907,6 +2907,108 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120416863</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>527854</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7167615</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23555-2024 artfynd.xlsx
+++ b/artfynd/A 23555-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117617763</v>
+        <v>117617792</v>
       </c>
       <c r="B2" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527908</v>
+        <v>527833</v>
       </c>
       <c r="R2" t="n">
-        <v>7167670</v>
+        <v>7167696</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117617801</v>
+        <v>117617742</v>
       </c>
       <c r="B3" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527821</v>
+        <v>527756</v>
       </c>
       <c r="R3" t="n">
-        <v>7167822</v>
+        <v>7167874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117617814</v>
+        <v>117617751</v>
       </c>
       <c r="B4" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527857</v>
+        <v>527589</v>
       </c>
       <c r="R4" t="n">
-        <v>7167609</v>
+        <v>7167810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117617761</v>
+        <v>117617744</v>
       </c>
       <c r="B5" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527640</v>
+        <v>527721</v>
       </c>
       <c r="R5" t="n">
-        <v>7167763</v>
+        <v>7167854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117617815</v>
+        <v>117617760</v>
       </c>
       <c r="B6" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527885</v>
+        <v>527651</v>
       </c>
       <c r="R6" t="n">
-        <v>7167588</v>
+        <v>7167777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117617773</v>
+        <v>117617761</v>
       </c>
       <c r="B7" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527758</v>
+        <v>527640</v>
       </c>
       <c r="R7" t="n">
-        <v>7167744</v>
+        <v>7167763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,53 +1317,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117617765</v>
+        <v>117617773</v>
       </c>
       <c r="B8" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527909</v>
+        <v>527758</v>
       </c>
       <c r="R8" t="n">
-        <v>7167663</v>
+        <v>7167744</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117617760</v>
+        <v>117617790</v>
       </c>
       <c r="B9" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527651</v>
+        <v>527840</v>
       </c>
       <c r="R9" t="n">
-        <v>7167777</v>
+        <v>7167691</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,55 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117617812</v>
+        <v>117617801</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527870</v>
+        <v>527821</v>
       </c>
       <c r="R10" t="n">
-        <v>7167648</v>
+        <v>7167822</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118682357</v>
+        <v>117617815</v>
       </c>
       <c r="B11" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1722,22 +1667,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527635</v>
+        <v>527885</v>
       </c>
       <c r="R11" t="n">
-        <v>7167757</v>
+        <v>7167588</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,12 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,43 +1727,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Andreas Estensen, Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118682186</v>
+        <v>118682060</v>
       </c>
       <c r="B12" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1842,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527828</v>
+        <v>527491</v>
       </c>
       <c r="R12" t="n">
-        <v>7167818</v>
+        <v>7167704</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,19 +1851,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682403</v>
+        <v>118682108</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1953,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527525</v>
+        <v>527477</v>
       </c>
       <c r="R13" t="n">
-        <v>7167728</v>
+        <v>7167550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,19 +1957,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118682108</v>
+        <v>118682186</v>
       </c>
       <c r="B14" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2064,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527477</v>
+        <v>527828</v>
       </c>
       <c r="R14" t="n">
-        <v>7167550</v>
+        <v>7167818</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2135,16 +2066,11 @@
         <v>118682328</v>
       </c>
       <c r="B15" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2243,19 +2169,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682840</v>
+        <v>118682357</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2286,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527463</v>
+        <v>527635</v>
       </c>
       <c r="R16" t="n">
-        <v>7167702</v>
+        <v>7167757</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2354,19 +2275,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118682719</v>
+        <v>118682382</v>
       </c>
       <c r="B17" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2397,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527409</v>
+        <v>527660</v>
       </c>
       <c r="R17" t="n">
-        <v>7167618</v>
+        <v>7167839</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,19 +2381,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682668</v>
+        <v>118682403</v>
       </c>
       <c r="B18" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2508,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527638</v>
+        <v>527525</v>
       </c>
       <c r="R18" t="n">
-        <v>7167796</v>
+        <v>7167728</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,19 +2487,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118682060</v>
+        <v>118682436</v>
       </c>
       <c r="B19" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2619,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527491</v>
+        <v>527722</v>
       </c>
       <c r="R19" t="n">
-        <v>7167704</v>
+        <v>7167844</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2690,16 +2596,11 @@
         <v>118682465</v>
       </c>
       <c r="B20" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2798,19 +2699,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118682436</v>
+        <v>118682668</v>
       </c>
       <c r="B21" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2841,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527722</v>
+        <v>527638</v>
       </c>
       <c r="R21" t="n">
-        <v>7167844</v>
+        <v>7167796</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2909,19 +2805,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120416863</v>
+        <v>118682719</v>
       </c>
       <c r="B22" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2943,19 +2834,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527854</v>
+        <v>527409</v>
       </c>
       <c r="R22" t="n">
-        <v>7167615</v>
+        <v>7167618</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2979,12 +2873,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,21 +2887,989 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118682840</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>527463</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7167702</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120416863</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>527854</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7167615</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>117617758</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>527608</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7167799</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117617812</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>527870</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7167648</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>117617797</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>527809</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7167693</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117617814</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>527857</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7167609</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117617756</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>527919</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7167684</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>117617763</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>527908</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7167670</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>117617765</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vindkraftparken, Bliekevare, Rajastrand, Ås lm., Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>527909</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7167663</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
